--- a/Output/Models/List_models_exposure_malf_iqr_by_sex.xlsx
+++ b/Output/Models/List_models_exposure_malf_iqr_by_sex.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
